--- a/data-source/磨尖武器数据.xlsx
+++ b/data-source/磨尖武器数据.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD354A4D-9E82-4CDD-9219-9812EAF992E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B09BFAF-15BC-4801-9A90-A3230A13F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>武器</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>蓝底为黑色系武器，数值与同名普通版本一致。</t>
+  </si>
+  <si>
+    <t>青铜矛</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1023,30 +1026,30 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5">
+        <v>65</v>
+      </c>
+      <c r="C19" s="5">
+        <v>72</v>
+      </c>
+      <c r="D19" s="5">
+        <v>78</v>
+      </c>
+      <c r="E19" s="5">
+        <v>91</v>
+      </c>
+      <c r="F19" s="5">
+        <v>107</v>
+      </c>
+      <c r="G19" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B19" s="5">
-        <v>67</v>
-      </c>
-      <c r="C19" s="5">
-        <v>74</v>
-      </c>
-      <c r="D19" s="5">
-        <v>81</v>
-      </c>
-      <c r="E19" s="5">
-        <v>94</v>
-      </c>
-      <c r="F19" s="5">
-        <v>111</v>
-      </c>
-      <c r="G19" s="5">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="B20" s="5">
         <v>67</v>
@@ -1068,31 +1071,31 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5">
+        <v>67</v>
+      </c>
+      <c r="C21" s="5">
+        <v>74</v>
+      </c>
+      <c r="D21" s="5">
+        <v>81</v>
+      </c>
+      <c r="E21" s="5">
+        <v>94</v>
+      </c>
+      <c r="F21" s="5">
+        <v>111</v>
+      </c>
+      <c r="G21" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B21" s="5">
-        <v>70</v>
-      </c>
-      <c r="C21" s="5">
-        <v>77</v>
-      </c>
-      <c r="D21" s="5">
-        <v>84</v>
-      </c>
-      <c r="E21" s="5">
-        <v>98</v>
-      </c>
-      <c r="F21" s="5">
-        <v>116</v>
-      </c>
-      <c r="G21" s="5">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="B22" s="5">
         <v>70</v>
@@ -1114,31 +1117,31 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="5">
+        <v>70</v>
+      </c>
+      <c r="C23" s="5">
+        <v>77</v>
+      </c>
+      <c r="D23" s="5">
+        <v>84</v>
+      </c>
+      <c r="E23" s="5">
+        <v>98</v>
+      </c>
+      <c r="F23" s="5">
+        <v>116</v>
+      </c>
+      <c r="G23" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B23" s="5">
-        <v>81</v>
-      </c>
-      <c r="C23" s="5">
-        <v>89</v>
-      </c>
-      <c r="D23" s="5">
-        <v>98</v>
-      </c>
-      <c r="E23" s="5">
-        <v>114</v>
-      </c>
-      <c r="F23" s="5">
-        <v>134</v>
-      </c>
-      <c r="G23" s="5">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="B24" s="5">
         <v>81</v>
@@ -1160,45 +1163,68 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="5">
+        <v>81</v>
+      </c>
+      <c r="C25" s="5">
+        <v>89</v>
+      </c>
+      <c r="D25" s="5">
+        <v>98</v>
+      </c>
+      <c r="E25" s="5">
+        <v>114</v>
+      </c>
+      <c r="F25" s="5">
+        <v>134</v>
+      </c>
+      <c r="G25" s="5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
         <v>90</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C26" s="5">
         <v>99</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D26" s="5">
         <v>108</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E26" s="5">
         <v>126</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F26" s="5">
         <v>149</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G26" s="5">
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="8" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="9" t="s">
         <v>41</v>
       </c>
     </row>

--- a/data-source/磨尖武器数据.xlsx
+++ b/data-source/磨尖武器数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B09BFAF-15BC-4801-9A90-A3230A13F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73576049-6700-40EA-8A7F-BABD0592AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>伤害倍率</t>
   </si>
   <si>
-    <t>未磨（—）</t>
-  </si>
-  <si>
     <t>磨1（100%）</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>青铜矛</t>
+  </si>
+  <si>
+    <t>白板（—）</t>
   </si>
 </sst>
 </file>
@@ -608,25 +608,25 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="J2" s="5">
         <v>1.1000000000000001</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5">
         <v>15</v>
@@ -655,7 +655,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
         <v>1.2</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5">
         <v>19</v>
@@ -684,7 +684,7 @@
         <v>38</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5">
         <v>1.4</v>
@@ -692,7 +692,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5">
         <v>21</v>
@@ -713,7 +713,7 @@
         <v>42</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="5">
         <v>1.65</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5">
         <v>21</v>
@@ -742,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" s="5">
         <v>2</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5">
         <v>30</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5">
         <v>33</v>
@@ -796,7 +796,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5">
         <v>36</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5">
         <v>40</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5">
         <v>40</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5">
         <v>43</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5">
         <v>58</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5">
         <v>59</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5">
         <v>59</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5">
         <v>61</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="5">
         <v>64</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5">
         <v>64</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5">
         <v>65</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5">
         <v>67</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5">
         <v>67</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5">
         <v>70</v>
@@ -1118,7 +1118,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5">
         <v>70</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="5">
         <v>81</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5">
         <v>81</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="5">
         <v>90</v>
@@ -1210,22 +1210,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/磨尖武器数据.xlsx
+++ b/data-source/磨尖武器数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73576049-6700-40EA-8A7F-BABD0592AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A68DE-6A26-451A-A15B-FA2B350405B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>武器</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>说明：</t>
-  </si>
-  <si>
-    <t>各级磨刀成功率独立判定，失败不累积。磨1 必定成功，磨2 起成功率依次为 70%、60%、50%、40%。</t>
   </si>
   <si>
     <t>伤害倍率以未磨为基准：磨1 为 1.1 倍，磨2 为 1.2 倍，磨3 为 1.4 倍，磨4 为 1.65 倍，磨5 为 2 倍。</t>
@@ -608,7 +605,7 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -1026,7 +1023,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5">
         <v>65</v>
@@ -1214,18 +1211,16 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="9" t="s">
-        <v>38</v>
-      </c>
+      <c r="A30" s="9"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
